--- a/results_(stress_test)_cross_valid/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-30_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_cross_valid/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-30_nm_basis-False_nm_modifier-False.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_cross_valid\results_(stress_test)_PCCxSigmoid-PLI-\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_BFE3C66C32C011436C226948C8DBF8D9A69D4C25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nrr_62" sheetId="1" r:id="rId1"/>
@@ -243,7 +243,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
